--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202610/Currency_P&L_20261007.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202610/Currency_P&L_20261007.xlsx
@@ -4249,31 +4249,67 @@
         <v>46302</v>
       </c>
       <c r="B89">
-        <v>92985678.3</v>
+        <v>94837053.37</v>
       </c>
       <c r="C89">
-        <v>-6431.26</v>
+        <v>-6687.11</v>
       </c>
       <c r="D89">
-        <v>-6.7E-05</v>
+        <v>-6.999999999999999E-05</v>
       </c>
       <c r="E89">
-        <v>-10835.92</v>
+        <v>-10918.15</v>
       </c>
       <c r="F89">
-        <v>-0.000113</v>
+        <v>-0.000114</v>
       </c>
       <c r="G89">
-        <v>-117709.59</v>
+        <v>-118434.6</v>
       </c>
       <c r="H89">
-        <v>-0.001232</v>
+        <v>-0.00124</v>
       </c>
       <c r="I89">
-        <v>-527804.73</v>
+        <v>-524398.89</v>
       </c>
       <c r="J89">
-        <v>-0.005526</v>
+        <v>-0.00549</v>
+      </c>
+      <c r="K89">
+        <v>-23.23</v>
+      </c>
+      <c r="L89">
+        <v>-0</v>
+      </c>
+      <c r="M89">
+        <v>-6695.39</v>
+      </c>
+      <c r="N89">
+        <v>-6.999999999999999E-05</v>
+      </c>
+      <c r="O89">
+        <v>-95.72</v>
+      </c>
+      <c r="P89">
+        <v>-1E-06</v>
+      </c>
+      <c r="S89">
+        <v>-472.18</v>
+      </c>
+      <c r="T89">
+        <v>-5E-06</v>
+      </c>
+      <c r="U89">
+        <v>14.76</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>122.45</v>
+      </c>
+      <c r="X89">
+        <v>1E-06</v>
       </c>
     </row>
   </sheetData>
